--- a/docs/design/06_認証認可設計書_HackerLake.xlsx
+++ b/docs/design/06_認証認可設計書_HackerLake.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\phrx4\hackerlake\docs\design\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{89A07229-8005-42B3-847F-D98ED36A35B1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{58BF6147-82AE-4CA3-816C-1FD41A67E13C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{451204CE-1BCF-4775-83D5-912DA7A34178}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{2D781052-5B45-47A3-92AF-4A70D6EC8762}"/>
   </bookViews>
   <sheets>
     <sheet name="表紙" sheetId="1" r:id="rId1"/>
@@ -18,6 +18,16 @@
     <sheet name="権限マトリクス" sheetId="3" r:id="rId3"/>
     <sheet name="将来状態遷移" sheetId="4" r:id="rId4"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">権限マトリクス!$A$3:$H$8</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">将来状態遷移!$A$3:$H$7</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">認証方針!$A$3:$H$8</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">表紙!$A$3:$H$6</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="2">権限マトリクス!$1:$3</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="3">将来状態遷移!$1:$3</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="1">認証方針!$1:$3</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="0">表紙!$1:$3</definedName>
+  </definedNames>
   <calcPr calcId="181029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -376,7 +386,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="5">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -403,15 +413,21 @@
     </font>
     <font>
       <b/>
-      <sz val="11"/>
+      <sz val="10"/>
       <color rgb="FFFFFFFF"/>
-      <name val="游ゴシック"/>
+      <name val="Yu Gothic"/>
       <family val="3"/>
       <charset val="128"/>
-      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Yu Gothic"/>
+      <family val="3"/>
+      <charset val="128"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -427,6 +443,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF006080"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF7FAFC"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -460,7 +482,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -468,12 +490,15 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -789,18 +814,22 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3D44E03F-4466-4A0E-98D2-9C076E4DC8A1}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B025CB70-2FDD-4827-9F80-60F1739D86FD}">
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
   <dimension ref="A1:H6"/>
-  <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultRowHeight="18.75"/>
   <cols>
-    <col min="1" max="1" width="16.625" customWidth="1"/>
-    <col min="2" max="2" width="24.625" customWidth="1"/>
-    <col min="3" max="3" width="34.625" customWidth="1"/>
-    <col min="4" max="5" width="42.625" customWidth="1"/>
-    <col min="6" max="8" width="28.625" customWidth="1"/>
+    <col min="1" max="1" width="15.625" customWidth="1"/>
+    <col min="2" max="2" width="22.625" customWidth="1"/>
+    <col min="3" max="3" width="36.625" customWidth="1"/>
+    <col min="4" max="5" width="46.625" customWidth="1"/>
+    <col min="6" max="7" width="28.625" customWidth="1"/>
+    <col min="8" max="8" width="24.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="27.95" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:8" ht="27.95" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -812,7 +841,7 @@
       <c r="G1" s="1"/>
       <c r="H1" s="1"/>
     </row>
-    <row r="3" spans="1:8" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:8" ht="32.1" customHeight="1">
       <c r="A3" s="2" t="s">
         <v>1</v>
       </c>
@@ -838,7 +867,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="4" spans="1:8" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:8" ht="33.950000000000003" customHeight="1">
       <c r="A4" s="3" t="s">
         <v>9</v>
       </c>
@@ -856,33 +885,33 @@
       <c r="G4" s="3"/>
       <c r="H4" s="3"/>
     </row>
-    <row r="5" spans="1:8" ht="42" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A5" s="3" t="s">
+    <row r="5" spans="1:8" ht="33.950000000000003" customHeight="1">
+      <c r="A5" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="B5" s="4">
+      <c r="B5" s="5">
         <v>46186</v>
       </c>
-      <c r="C5" s="3" t="s">
+      <c r="C5" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="D5" s="3" t="s">
+      <c r="D5" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="E5" s="3" t="s">
+      <c r="E5" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="F5" s="3" t="s">
+      <c r="F5" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="G5" s="3" t="s">
+      <c r="G5" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="H5" s="3" t="s">
+      <c r="H5" s="4" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="6" spans="1:8" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:8" ht="33.950000000000003" customHeight="1">
       <c r="A6" s="3" t="s">
         <v>20</v>
       </c>
@@ -909,27 +938,33 @@
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A3:H6" xr:uid="{B025CB70-2FDD-4827-9F80-60F1739D86FD}"/>
   <mergeCells count="1">
     <mergeCell ref="A1:H1"/>
   </mergeCells>
   <phoneticPr fontId="1"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageMargins left="0.3" right="0.3" top="0.44999999999999996" bottom="0.44999999999999996" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" scale="52" fitToHeight="0" orientation="landscape" r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A8A1FF73-DB06-41F8-AF35-7684201CA3B9}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1DABFBD4-0B2F-4AE7-B620-C79A05DC3993}">
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
   <dimension ref="A1:H8"/>
-  <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultRowHeight="18.75"/>
   <cols>
-    <col min="1" max="1" width="16.625" customWidth="1"/>
-    <col min="2" max="2" width="24.625" customWidth="1"/>
-    <col min="3" max="3" width="34.625" customWidth="1"/>
-    <col min="4" max="5" width="42.625" customWidth="1"/>
-    <col min="6" max="8" width="28.625" customWidth="1"/>
+    <col min="1" max="1" width="15.625" customWidth="1"/>
+    <col min="2" max="2" width="22.625" customWidth="1"/>
+    <col min="3" max="3" width="36.625" customWidth="1"/>
+    <col min="4" max="5" width="46.625" customWidth="1"/>
+    <col min="6" max="7" width="28.625" customWidth="1"/>
+    <col min="8" max="8" width="24.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="27.95" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:8" ht="27.95" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>28</v>
       </c>
@@ -941,7 +976,7 @@
       <c r="G1" s="1"/>
       <c r="H1" s="1"/>
     </row>
-    <row r="3" spans="1:8" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:8" ht="32.1" customHeight="1">
       <c r="A3" s="2" t="s">
         <v>29</v>
       </c>
@@ -967,7 +1002,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="4" spans="1:8" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:8" ht="33.950000000000003" customHeight="1">
       <c r="A4" s="3" t="s">
         <v>37</v>
       </c>
@@ -993,31 +1028,31 @@
         <v>43</v>
       </c>
     </row>
-    <row r="5" spans="1:8" ht="42" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A5" s="3" t="s">
+    <row r="5" spans="1:8" ht="33.950000000000003" customHeight="1">
+      <c r="A5" s="4" t="s">
         <v>44</v>
       </c>
-      <c r="B5" s="3" t="s">
+      <c r="B5" s="4" t="s">
         <v>45</v>
       </c>
-      <c r="C5" s="3" t="s">
+      <c r="C5" s="4" t="s">
         <v>46</v>
       </c>
-      <c r="D5" s="3" t="s">
+      <c r="D5" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="E5" s="3" t="s">
+      <c r="E5" s="4" t="s">
         <v>48</v>
       </c>
-      <c r="F5" s="3" t="s">
+      <c r="F5" s="4" t="s">
         <v>49</v>
       </c>
-      <c r="G5" s="3" t="s">
+      <c r="G5" s="4" t="s">
         <v>50</v>
       </c>
-      <c r="H5" s="3"/>
-    </row>
-    <row r="6" spans="1:8" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="H5" s="4"/>
+    </row>
+    <row r="6" spans="1:8" ht="33.950000000000003" customHeight="1">
       <c r="A6" s="3" t="s">
         <v>51</v>
       </c>
@@ -1041,31 +1076,31 @@
       </c>
       <c r="H6" s="3"/>
     </row>
-    <row r="7" spans="1:8" ht="42" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A7" s="3" t="s">
+    <row r="7" spans="1:8" ht="33.950000000000003" customHeight="1">
+      <c r="A7" s="4" t="s">
         <v>58</v>
       </c>
-      <c r="B7" s="3" t="s">
+      <c r="B7" s="4" t="s">
         <v>59</v>
       </c>
-      <c r="C7" s="3" t="s">
+      <c r="C7" s="4" t="s">
         <v>60</v>
       </c>
-      <c r="D7" s="3" t="s">
+      <c r="D7" s="4" t="s">
         <v>61</v>
       </c>
-      <c r="E7" s="3" t="s">
+      <c r="E7" s="4" t="s">
         <v>62</v>
       </c>
-      <c r="F7" s="3" t="s">
+      <c r="F7" s="4" t="s">
         <v>63</v>
       </c>
-      <c r="G7" s="3" t="s">
+      <c r="G7" s="4" t="s">
         <v>57</v>
       </c>
-      <c r="H7" s="3"/>
-    </row>
-    <row r="8" spans="1:8" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="H7" s="4"/>
+    </row>
+    <row r="8" spans="1:8" ht="33.950000000000003" customHeight="1">
       <c r="A8" s="3" t="s">
         <v>64</v>
       </c>
@@ -1090,27 +1125,33 @@
       <c r="H8" s="3"/>
     </row>
   </sheetData>
+  <autoFilter ref="A3:H8" xr:uid="{1DABFBD4-0B2F-4AE7-B620-C79A05DC3993}"/>
   <mergeCells count="1">
     <mergeCell ref="A1:H1"/>
   </mergeCells>
   <phoneticPr fontId="1"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageMargins left="0.3" right="0.3" top="0.44999999999999996" bottom="0.44999999999999996" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" scale="52" fitToHeight="0" orientation="landscape" r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D9664F8D-BD4D-44DE-A75D-B84BEA1EB150}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0AAD1F0C-869B-4D1A-B63A-3855D332BC02}">
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
   <dimension ref="A1:H8"/>
-  <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultRowHeight="18.75"/>
   <cols>
-    <col min="1" max="1" width="16.625" customWidth="1"/>
-    <col min="2" max="2" width="24.625" customWidth="1"/>
-    <col min="3" max="3" width="34.625" customWidth="1"/>
-    <col min="4" max="5" width="42.625" customWidth="1"/>
-    <col min="6" max="8" width="28.625" customWidth="1"/>
+    <col min="1" max="1" width="15.625" customWidth="1"/>
+    <col min="2" max="2" width="22.625" customWidth="1"/>
+    <col min="3" max="3" width="36.625" customWidth="1"/>
+    <col min="4" max="5" width="46.625" customWidth="1"/>
+    <col min="6" max="7" width="28.625" customWidth="1"/>
+    <col min="8" max="8" width="24.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="27.95" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:8" ht="27.95" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>70</v>
       </c>
@@ -1122,7 +1163,7 @@
       <c r="G1" s="1"/>
       <c r="H1" s="1"/>
     </row>
-    <row r="3" spans="1:8" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:8" ht="32.1" customHeight="1">
       <c r="A3" s="2" t="s">
         <v>71</v>
       </c>
@@ -1148,7 +1189,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="4" spans="1:8" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:8" ht="33.950000000000003" customHeight="1">
       <c r="A4" s="3" t="s">
         <v>75</v>
       </c>
@@ -1172,33 +1213,33 @@
       </c>
       <c r="H4" s="3"/>
     </row>
-    <row r="5" spans="1:8" ht="42" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A5" s="3" t="s">
+    <row r="5" spans="1:8" ht="33.950000000000003" customHeight="1">
+      <c r="A5" s="4" t="s">
         <v>79</v>
       </c>
-      <c r="B5" s="3" t="s">
+      <c r="B5" s="4" t="s">
         <v>76</v>
       </c>
-      <c r="C5" s="3" t="s">
+      <c r="C5" s="4" t="s">
         <v>76</v>
       </c>
-      <c r="D5" s="3" t="s">
+      <c r="D5" s="4" t="s">
         <v>76</v>
       </c>
-      <c r="E5" s="3" t="s">
+      <c r="E5" s="4" t="s">
         <v>76</v>
       </c>
-      <c r="F5" s="3" t="s">
+      <c r="F5" s="4" t="s">
         <v>77</v>
       </c>
-      <c r="G5" s="3" t="s">
+      <c r="G5" s="4" t="s">
         <v>78</v>
       </c>
-      <c r="H5" s="3" t="s">
+      <c r="H5" s="4" t="s">
         <v>80</v>
       </c>
     </row>
-    <row r="6" spans="1:8" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:8" ht="33.950000000000003" customHeight="1">
       <c r="A6" s="3" t="s">
         <v>81</v>
       </c>
@@ -1222,31 +1263,31 @@
       </c>
       <c r="H6" s="3"/>
     </row>
-    <row r="7" spans="1:8" ht="42" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A7" s="3" t="s">
+    <row r="7" spans="1:8" ht="33.950000000000003" customHeight="1">
+      <c r="A7" s="4" t="s">
         <v>84</v>
       </c>
-      <c r="B7" s="3" t="s">
+      <c r="B7" s="4" t="s">
         <v>82</v>
       </c>
-      <c r="C7" s="3" t="s">
+      <c r="C7" s="4" t="s">
         <v>82</v>
       </c>
-      <c r="D7" s="3" t="s">
+      <c r="D7" s="4" t="s">
         <v>76</v>
       </c>
-      <c r="E7" s="3" t="s">
+      <c r="E7" s="4" t="s">
         <v>76</v>
       </c>
-      <c r="F7" s="3" t="s">
+      <c r="F7" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="G7" s="3" t="s">
+      <c r="G7" s="4" t="s">
         <v>85</v>
       </c>
-      <c r="H7" s="3"/>
-    </row>
-    <row r="8" spans="1:8" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="H7" s="4"/>
+    </row>
+    <row r="8" spans="1:8" ht="33.950000000000003" customHeight="1">
       <c r="A8" s="3" t="s">
         <v>86</v>
       </c>
@@ -1271,27 +1312,33 @@
       <c r="H8" s="3"/>
     </row>
   </sheetData>
+  <autoFilter ref="A3:H8" xr:uid="{0AAD1F0C-869B-4D1A-B63A-3855D332BC02}"/>
   <mergeCells count="1">
     <mergeCell ref="A1:H1"/>
   </mergeCells>
   <phoneticPr fontId="1"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageMargins left="0.3" right="0.3" top="0.44999999999999996" bottom="0.44999999999999996" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" scale="52" fitToHeight="0" orientation="landscape" r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FE99429B-DB94-4081-8639-C0590A4713C9}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5623DE57-CF9B-4B50-98EA-0D567262D861}">
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
   <dimension ref="A1:H7"/>
-  <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultRowHeight="18.75"/>
   <cols>
-    <col min="1" max="1" width="16.625" customWidth="1"/>
-    <col min="2" max="2" width="24.625" customWidth="1"/>
-    <col min="3" max="3" width="34.625" customWidth="1"/>
-    <col min="4" max="5" width="42.625" customWidth="1"/>
-    <col min="6" max="8" width="28.625" customWidth="1"/>
+    <col min="1" max="1" width="15.625" customWidth="1"/>
+    <col min="2" max="2" width="22.625" customWidth="1"/>
+    <col min="3" max="3" width="36.625" customWidth="1"/>
+    <col min="4" max="5" width="46.625" customWidth="1"/>
+    <col min="6" max="7" width="28.625" customWidth="1"/>
+    <col min="8" max="8" width="24.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="27.95" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:8" ht="27.95" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>88</v>
       </c>
@@ -1303,7 +1350,7 @@
       <c r="G1" s="1"/>
       <c r="H1" s="1"/>
     </row>
-    <row r="3" spans="1:8" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:8" ht="32.1" customHeight="1">
       <c r="A3" s="2" t="s">
         <v>31</v>
       </c>
@@ -1329,7 +1376,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="4" spans="1:8" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:8" ht="33.950000000000003" customHeight="1">
       <c r="A4" s="3" t="s">
         <v>45</v>
       </c>
@@ -1355,33 +1402,33 @@
         <v>57</v>
       </c>
     </row>
-    <row r="5" spans="1:8" ht="42" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A5" s="3" t="s">
+    <row r="5" spans="1:8" ht="33.950000000000003" customHeight="1">
+      <c r="A5" s="4" t="s">
         <v>100</v>
       </c>
-      <c r="B5" s="3" t="s">
+      <c r="B5" s="4" t="s">
         <v>101</v>
       </c>
-      <c r="C5" s="3" t="s">
+      <c r="C5" s="4" t="s">
         <v>102</v>
       </c>
-      <c r="D5" s="3" t="s">
+      <c r="D5" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="E5" s="3" t="s">
+      <c r="E5" s="4" t="s">
         <v>104</v>
       </c>
-      <c r="F5" s="3" t="s">
+      <c r="F5" s="4" t="s">
         <v>56</v>
       </c>
-      <c r="G5" s="3" t="s">
+      <c r="G5" s="4" t="s">
         <v>99</v>
       </c>
-      <c r="H5" s="3" t="s">
+      <c r="H5" s="4" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="6" spans="1:8" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:8" ht="33.950000000000003" customHeight="1">
       <c r="A6" s="3" t="s">
         <v>105</v>
       </c>
@@ -1407,37 +1454,39 @@
         <v>57</v>
       </c>
     </row>
-    <row r="7" spans="1:8" ht="42" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A7" s="3" t="s">
+    <row r="7" spans="1:8" ht="33.950000000000003" customHeight="1">
+      <c r="A7" s="4" t="s">
         <v>110</v>
       </c>
-      <c r="B7" s="3" t="s">
+      <c r="B7" s="4" t="s">
         <v>111</v>
       </c>
-      <c r="C7" s="3" t="s">
+      <c r="C7" s="4" t="s">
         <v>112</v>
       </c>
-      <c r="D7" s="3" t="s">
+      <c r="D7" s="4" t="s">
         <v>100</v>
       </c>
-      <c r="E7" s="3" t="s">
+      <c r="E7" s="4" t="s">
         <v>113</v>
       </c>
-      <c r="F7" s="3" t="s">
+      <c r="F7" s="4" t="s">
         <v>56</v>
       </c>
-      <c r="G7" s="3" t="s">
+      <c r="G7" s="4" t="s">
         <v>99</v>
       </c>
-      <c r="H7" s="3" t="s">
+      <c r="H7" s="4" t="s">
         <v>57</v>
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A3:H7" xr:uid="{5623DE57-CF9B-4B50-98EA-0D567262D861}"/>
   <mergeCells count="1">
     <mergeCell ref="A1:H1"/>
   </mergeCells>
   <phoneticPr fontId="1"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageMargins left="0.3" right="0.3" top="0.44999999999999996" bottom="0.44999999999999996" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" scale="52" fitToHeight="0" orientation="landscape" r:id="rId1"/>
 </worksheet>
 </file>